--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487907_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487907_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9821</v>
+        <v>6.2792</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3855</v>
+        <v>8.0937</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4034</v>
+        <v>-1.8145</v>
       </c>
       <c r="G2" t="n">
         <v>0.8119</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6217</v>
+        <v>-0.3246</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8358</v>
+        <v>-0.1276</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2141</v>
+        <v>-0.197</v>
       </c>
       <c r="V2" t="n">
         <v>3.5026</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0882</v>
+        <v>2.2713</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9433</v>
+        <v>1.966</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8551</v>
+        <v>0.3053</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6891</v>
+        <v>1.365</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-1.8231</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6891</v>
+        <v>3.1881</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6734</v>
+        <v>2.0794</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0657</v>
+        <v>-2.1047</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6076</v>
+        <v>4.1842</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9843</v>
+        <v>-0.7144</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0657</v>
+        <v>0.2816</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9186</v>
+        <v>-0.996</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0812</v>
+        <v>-0.2081</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7055</v>
+        <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0662</v>
+        <v>-0.3642</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8912</v>
+        <v>-0.1352</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1749</v>
+        <v>-0.229</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2914</v>
+        <v>0.23</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4599</v>
+        <v>0.23</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9792</v>
+        <v>0.7986</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6445</v>
+        <v>2.8299</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3347</v>
+        <v>-2.0313</v>
       </c>
       <c r="G4" t="n">
-        <v>1.365</v>
+        <v>0.6891</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8231</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1881</v>
+        <v>0.6891</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0794</v>
+        <v>3.6734</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.1047</v>
+        <v>1.0657</v>
       </c>
       <c r="L4" t="n">
-        <v>4.1842</v>
+        <v>2.6076</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7144</v>
+        <v>-2.9843</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2816</v>
+        <v>-1.0657</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.996</v>
+        <v>-1.9186</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2081</v>
+        <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2487</v>
+        <v>2.7055</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6563</v>
+        <v>0.7765</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4567</v>
+        <v>0.7778</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1996</v>
+        <v>-0.0012</v>
       </c>
       <c r="V4" t="n">
-        <v>0.23</v>
+        <v>-1.2914</v>
       </c>
       <c r="W4" t="n">
-        <v>0.23</v>
+        <v>0.4599</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2947</v>
+        <v>0.4202</v>
       </c>
       <c r="E5" t="n">
-        <v>1.08</v>
+        <v>0.8238</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7853</v>
+        <v>-0.4036</v>
       </c>
       <c r="G5" t="n">
         <v>1.3424</v>
@@ -844,13 +844,13 @@
         <v>2.4974</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3204</v>
+        <v>-0.1949</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4625</v>
+        <v>0.2063</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.4012</v>
       </c>
       <c r="V5" t="n">
         <v>0.9376</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. SOAREZ PEREYRA</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2435</v>
+        <v>-0.0696</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1765</v>
+        <v>1.4006</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.067</v>
+        <v>-1.4703</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0559</v>
+        <v>-0.9386</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4478</v>
+        <v>-2.787</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3919</v>
+        <v>1.8484</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0192</v>
+        <v>2.0538</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0192</v>
+        <v>-2.2479</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.3017</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0367</v>
+        <v>-2.9924</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4286</v>
+        <v>-0.5391</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3919</v>
+        <v>-2.4533</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2995</v>
+        <v>-0.4224</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1957</v>
+        <v>-0.3233</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1037</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2914</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>S. SOAREZ PEREYRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7778</v>
+        <v>-0.1848</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6924</v>
+        <v>-0.1765</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4703</v>
+        <v>-0.0083</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9386</v>
+        <v>0.0559</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.787</v>
+        <v>0.4478</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8484</v>
+        <v>-0.3919</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0538</v>
+        <v>0.0192</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.2479</v>
+        <v>0.0192</v>
       </c>
       <c r="L7" t="n">
-        <v>4.3017</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9924</v>
+        <v>0.0367</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5391</v>
+        <v>0.4286</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.4533</v>
+        <v>-0.3919</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0812</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1306</v>
+        <v>-0.2407</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0315</v>
+        <v>-0.1957</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.045</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2914</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1293</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2726</v>
+        <v>-1.1655</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1434</v>
+        <v>0.4663</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0582</v>
@@ -1078,13 +1078,13 @@
         <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4249</v>
+        <v>-0.9948</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5252</v>
+        <v>-0.4181</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8996</v>
+        <v>-0.5767</v>
       </c>
       <c r="V8" t="n">
         <v>0.9376</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8547</v>
+        <v>-1.4745</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8767</v>
+        <v>-2.5552</v>
       </c>
       <c r="F9" t="n">
-        <v>1.022</v>
+        <v>1.0807</v>
       </c>
       <c r="G9" t="n">
         <v>-2.102</v>
@@ -1156,13 +1156,13 @@
         <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.205</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6524</v>
+        <v>-0.331</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0672</v>
+        <v>0.1259</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5366</v>
+        <v>-2.1564</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5586</v>
+        <v>-0.2371</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.978</v>
+        <v>-1.9193</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4206</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9891</v>
+        <v>-0.6089</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5219</v>
+        <v>-0.2005</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4671</v>
+        <v>-0.4084</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4579</v>
+        <v>-7.5141</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2578</v>
+        <v>-5.0498</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2</v>
+        <v>-2.4643</v>
       </c>
       <c r="G11" t="n">
         <v>-5.5421</v>
@@ -1312,13 +1312,13 @@
         <v>1.8731</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2278</v>
+        <v>0.1716</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8539</v>
+        <v>0.0619</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3739</v>
+        <v>0.1096</v>
       </c>
       <c r="V11" t="n">
         <v>0.3538</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6556</v>
+        <v>-2.329200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>5.6035</v>
+        <v>5.929899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.259</v>
+        <v>-8.2593</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.7972</v>
+        <v>-6.797199999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-2.1638</v>
@@ -1366,7 +1366,7 @@
         <v>11.7372</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8764999999999996</v>
+        <v>-0.8765000000000001</v>
       </c>
       <c r="L12" t="n">
         <v>12.6135</v>
@@ -1390,13 +1390,13 @@
         <v>16.6494</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.733700000000001</v>
+        <v>-2.4074</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0116</v>
+        <v>-0.6854</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7218</v>
+        <v>-1.7221</v>
       </c>
       <c r="V12" t="n">
         <v>4.7941</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.325</v>
+        <v>6.3354</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4775</v>
+        <v>6.2276</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1524</v>
+        <v>0.1079</v>
       </c>
       <c r="G13" t="n">
         <v>5.6311</v>
@@ -1468,13 +1468,13 @@
         <v>2.2893</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.869</v>
+        <v>0.1414</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7053</v>
+        <v>0.0448</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1637</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4776</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1524</v>
+        <v>4.0794</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4512</v>
+        <v>3.5583</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7012</v>
+        <v>0.5211</v>
       </c>
       <c r="G14" t="n">
         <v>3.51</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2819</v>
+        <v>0.2089</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0562</v>
+        <v>0.051</v>
       </c>
       <c r="U14" t="n">
-        <v>0.338</v>
+        <v>0.1579</v>
       </c>
       <c r="V14" t="n">
         <v>1.401</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0581</v>
+        <v>2.4397</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6571</v>
+        <v>2.6932</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5991</v>
+        <v>-0.2534</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3567</v>
+        <v>2.0402</v>
       </c>
       <c r="H15" t="n">
-        <v>0.356</v>
+        <v>-1.966</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7127</v>
+        <v>4.0062</v>
       </c>
       <c r="J15" t="n">
-        <v>0.766</v>
+        <v>3.2077</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4133</v>
+        <v>-1.721</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3527</v>
+        <v>4.9287</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1227</v>
+        <v>-1.1676</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0573</v>
+        <v>-0.245</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0654</v>
+        <v>-0.9225</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9326</v>
+        <v>0.1848</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3479</v>
+        <v>0.1691</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5846</v>
+        <v>0.0157</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9340000000000001</v>
+        <v>1.0472</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5178</v>
+        <v>-0.3503</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.867</v>
+        <v>1.6718</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1217</v>
+        <v>1.0146</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7453</v>
+        <v>0.6572</v>
       </c>
       <c r="G16" t="n">
         <v>0.5901999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.488</v>
+        <v>0.2928</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1396</v>
+        <v>0.0324</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3484</v>
+        <v>0.2604</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4599</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5516</v>
+        <v>1.6398</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1574</v>
+        <v>0.0075</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6058</v>
+        <v>1.6323</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0402</v>
+        <v>1.6925</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.966</v>
+        <v>1.0426</v>
       </c>
       <c r="I17" t="n">
-        <v>4.0062</v>
+        <v>0.6499</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2077</v>
+        <v>0.6924</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.721</v>
+        <v>0.614</v>
       </c>
       <c r="L17" t="n">
-        <v>4.9287</v>
+        <v>0.0784</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1676</v>
+        <v>1.0001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.245</v>
+        <v>0.4286</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9225</v>
+        <v>0.5715</v>
       </c>
       <c r="P17" t="n">
         <v>-0.8325</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7033</v>
+        <v>0.5498</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3667</v>
+        <v>0.1257</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3366</v>
+        <v>0.4241</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0472</v>
+        <v>0.23</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3503</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2596</v>
+        <v>0.4262</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.314</v>
+        <v>1.2641</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5736</v>
+        <v>-0.8379</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6925</v>
+        <v>-0.3567</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0426</v>
+        <v>0.356</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6499</v>
+        <v>-0.7127</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6924</v>
+        <v>0.766</v>
       </c>
       <c r="K18" t="n">
-        <v>0.614</v>
+        <v>0.4133</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0784</v>
+        <v>0.3527</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0001</v>
+        <v>-1.1227</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4286</v>
+        <v>-0.0573</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5715</v>
+        <v>-1.0654</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1696</v>
+        <v>1.3007</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1957</v>
+        <v>0.9549</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3654</v>
+        <v>0.3458</v>
       </c>
       <c r="V18" t="n">
-        <v>0.23</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>0.23</v>
+        <v>0.5838</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.5178</v>
       </c>
     </row>
     <row r="19">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0421</v>
+        <v>0.1722</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1265</v>
+        <v>-0.9122</v>
       </c>
       <c r="F19" t="n">
         <v>1.0844</v>
@@ -1936,10 +1936,10 @@
         <v>1.8731</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2205</v>
+        <v>0.4348</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1396</v>
+        <v>0.3539</v>
       </c>
       <c r="U19" t="n">
         <v>0.0809</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8536</v>
+        <v>-1.8179</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2281</v>
+        <v>-0.3352</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6255</v>
+        <v>-1.4827</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4945</v>
@@ -2014,13 +2014,13 @@
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3262</v>
+        <v>0.3619</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1396</v>
+        <v>0.0324</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1866</v>
+        <v>0.3295</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5178</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1899</v>
+        <v>-2.1019</v>
       </c>
       <c r="E21" t="n">
         <v>0.0172</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2071</v>
+        <v>-2.119</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2205</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3451</v>
+        <v>-0.2571</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1181</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.227</v>
+        <v>-0.139</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7222</v>
+        <v>-4.6572</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1932</v>
+        <v>-2.3003</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5291</v>
+        <v>-2.3568</v>
       </c>
       <c r="G22" t="n">
         <v>-1.419</v>
@@ -2170,13 +2170,13 @@
         <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.1375</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1924</v>
+        <v>0.0853</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.12</v>
+        <v>0.0522</v>
       </c>
       <c r="V22" t="n">
         <v>-2.3351</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7311</v>
+        <v>-4.7986</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.742</v>
+        <v>-2.9563</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9891</v>
+        <v>-1.8423</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1432</v>
@@ -2248,13 +2248,13 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1598</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2048</v>
+        <v>-0.0095</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.045</v>
+        <v>0.1018</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7477</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.6748</v>
+        <v>3.388899999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>8.278299999999998</v>
+        <v>8.278500000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.6036</v>
+        <v>-4.8892</v>
       </c>
       <c r="G24" t="n">
-        <v>6.816199999999998</v>
+        <v>6.8162</v>
       </c>
       <c r="H24" t="n">
         <v>2.183</v>
@@ -2326,13 +2326,13 @@
         <v>14.5683</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7336</v>
+        <v>3.4478</v>
       </c>
       <c r="T24" t="n">
         <v>1.7219</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0116</v>
+        <v>1.7259</v>
       </c>
       <c r="V24" t="n">
         <v>-4.793900000000001</v>
